--- a/packages/GB Accounts Company 2027-08-31 (Aug27) Excel 2007/expensesform.xlsx
+++ b/packages/GB Accounts Company 2027-08-31 (Aug27) Excel 2007/expensesform.xlsx
@@ -1653,7 +1653,7 @@
         <v>Mileage Claim @ 45p</v>
       </c>
       <c r="C30" s="15">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="7">
         <f>SUM(D10:D29)</f>
